--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20261021.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20261021.xlsx
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>潤弘</t>
+          <t>裕融</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>14,390,000</t>
+          <t>31,138,800</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>裕融</t>
+          <t>潤弘</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>31,138,800</t>
+          <t>14,390,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>202611TX</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>台指期</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>41,700,000</t>
+          <t>228</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>202611TX</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>台指期</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>41,700,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
